--- a/outputs/82-30.xlsx
+++ b/outputs/82-30.xlsx
@@ -92,8 +92,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -290,350 +294,350 @@
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="n">
+      <c r="A1" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B1" s="0" t="n">
+      <c r="B1" s="1" t="n">
         <v>0.0253968253968254</v>
       </c>
-      <c r="C1" s="0" t="n">
+      <c r="C1" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="D1" s="0" t="n">
+      <c r="D1" s="1" t="n">
         <v>0.0158730158730159</v>
       </c>
-      <c r="E1" s="0" t="n">
+      <c r="E1" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="F1" s="0" t="n">
+      <c r="F1" s="1" t="n">
         <v>0.0222222222222222</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>41</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="1" t="n">
         <v>0.0190476190476191</v>
       </c>
-      <c r="C2" s="0" t="n">
+      <c r="C2" s="1" t="n">
         <v>52</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2" s="1" t="n">
         <v>0.0158730158730159</v>
       </c>
-      <c r="E2" s="0" t="n">
+      <c r="E2" s="1" t="n">
         <v>48</v>
       </c>
-      <c r="F2" s="0" t="n">
+      <c r="F2" s="1" t="n">
         <v>0.0206349206349206</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="1" t="n">
         <v>0.0222222222222222</v>
       </c>
-      <c r="C3" s="0" t="n">
+      <c r="C3" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="D3" s="0" t="n">
+      <c r="D3" s="1" t="n">
         <v>0.0206349206349206</v>
       </c>
-      <c r="E3" s="0" t="n">
+      <c r="E3" s="1" t="n">
         <v>49</v>
       </c>
-      <c r="F3" s="0" t="n">
+      <c r="F3" s="1" t="n">
         <v>0.0158730158730159</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="1" t="n">
         <v>0.0174603174603175</v>
       </c>
-      <c r="C4" s="0" t="n">
+      <c r="C4" s="1" t="n">
         <v>42</v>
       </c>
-      <c r="D4" s="0" t="n">
+      <c r="D4" s="1" t="n">
         <v>0.0174603174603175</v>
       </c>
-      <c r="E4" s="0" t="n">
+      <c r="E4" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="F4" s="0" t="n">
+      <c r="F4" s="1" t="n">
         <v>0.0174603174603175</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="1" t="n">
         <v>0.0253968253968254</v>
       </c>
-      <c r="C5" s="0" t="n">
+      <c r="C5" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="D5" s="0" t="n">
+      <c r="D5" s="1" t="n">
         <v>0.0206349206349206</v>
       </c>
-      <c r="E5" s="0" t="n">
+      <c r="E5" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="F5" s="0" t="n">
+      <c r="F5" s="1" t="n">
         <v>0.0238095238095238</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="1" t="n">
         <v>0.0190476190476191</v>
       </c>
-      <c r="C6" s="0" t="n">
+      <c r="C6" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="D6" s="0" t="n">
+      <c r="D6" s="1" t="n">
         <v>0.0190476190476191</v>
       </c>
-      <c r="E6" s="0" t="n">
+      <c r="E6" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="F6" s="0" t="n">
+      <c r="F6" s="1" t="n">
         <v>0.0142857142857143</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="1" t="n">
         <v>38</v>
       </c>
-      <c r="B7" s="0" t="n">
+      <c r="B7" s="1" t="n">
         <v>0.0253968253968254</v>
       </c>
-      <c r="C7" s="0" t="n">
+      <c r="C7" s="1" t="n">
         <v>37</v>
       </c>
-      <c r="D7" s="0" t="n">
+      <c r="D7" s="1" t="n">
         <v>0.0222222222222222</v>
       </c>
-      <c r="E7" s="0" t="n">
+      <c r="E7" s="1" t="n">
         <v>46</v>
       </c>
-      <c r="F7" s="0" t="n">
+      <c r="F7" s="1" t="n">
         <v>0.0238095238095238</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+      <c r="A8" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="B8" s="0" t="n">
+      <c r="B8" s="1" t="n">
         <v>0.0206349206349206</v>
       </c>
-      <c r="C8" s="0" t="n">
+      <c r="C8" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="D8" s="0" t="n">
+      <c r="D8" s="1" t="n">
         <v>0.0190476190476191</v>
       </c>
-      <c r="E8" s="0" t="n">
+      <c r="E8" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="F8" s="0" t="n">
+      <c r="F8" s="1" t="n">
         <v>0.0206349206349206</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+      <c r="A9" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="0" t="n">
+      <c r="B9" s="1" t="n">
         <v>0.0206349206349206</v>
       </c>
-      <c r="C9" s="0" t="n">
+      <c r="C9" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D9" s="0" t="n">
+      <c r="D9" s="1" t="n">
         <v>0.0142857142857143</v>
       </c>
-      <c r="E9" s="0" t="n">
+      <c r="E9" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="F9" s="0" t="n">
+      <c r="F9" s="1" t="n">
         <v>0.0190476190476191</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
+      <c r="A10" s="1" t="n">
         <v>39</v>
       </c>
-      <c r="B10" s="0" t="n">
+      <c r="B10" s="1" t="n">
         <v>0.0206349206349206</v>
       </c>
-      <c r="C10" s="0" t="n">
+      <c r="C10" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="D10" s="0" t="n">
+      <c r="D10" s="1" t="n">
         <v>0.0253968253968254</v>
       </c>
-      <c r="E10" s="0" t="n">
+      <c r="E10" s="1" t="n">
         <v>44</v>
       </c>
-      <c r="F10" s="0" t="n">
+      <c r="F10" s="1" t="n">
         <v>0.0238095238095238</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
+      <c r="A11" s="1" t="n">
         <v>43</v>
       </c>
-      <c r="B11" s="0" t="n">
+      <c r="B11" s="1" t="n">
         <v>0.0158730158730159</v>
       </c>
-      <c r="C11" s="0" t="n">
+      <c r="C11" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="0" t="n">
+      <c r="D11" s="1" t="n">
         <v>0.0206349206349206</v>
       </c>
-      <c r="E11" s="0" t="n">
+      <c r="E11" s="1" t="n">
         <v>47</v>
       </c>
-      <c r="F11" s="0" t="n">
+      <c r="F11" s="1" t="n">
         <v>0.0174603174603175</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="n">
+      <c r="A12" s="1" t="n">
         <v>45</v>
       </c>
-      <c r="B12" s="0" t="n">
+      <c r="B12" s="1" t="n">
         <v>0.0238095238095238</v>
       </c>
-      <c r="C12" s="0" t="n">
+      <c r="C12" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="D12" s="0" t="n">
+      <c r="D12" s="1" t="n">
         <v>0.0158730158730159</v>
       </c>
-      <c r="E12" s="0" t="n">
+      <c r="E12" s="1" t="n">
         <v>33</v>
       </c>
-      <c r="F12" s="0" t="n">
+      <c r="F12" s="1" t="n">
         <v>0.0126984126984127</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="n">
+      <c r="A13" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="B13" s="0" t="n">
+      <c r="B13" s="1" t="n">
         <v>0.0111111111111111</v>
       </c>
-      <c r="C13" s="0" t="n">
+      <c r="C13" s="1" t="n">
         <v>29</v>
       </c>
-      <c r="D13" s="0" t="n">
+      <c r="D13" s="1" t="n">
         <v>0.0190476190476191</v>
       </c>
-      <c r="E13" s="0" t="n">
+      <c r="E13" s="1" t="n">
         <v>51</v>
       </c>
-      <c r="F13" s="0" t="n">
+      <c r="F13" s="1" t="n">
         <v>0.0190476190476191</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="n">
+      <c r="A14" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="B14" s="0" t="n">
+      <c r="B14" s="1" t="n">
         <v>0.0174603174603175</v>
       </c>
-      <c r="C14" s="0" t="n">
+      <c r="C14" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="D14" s="0" t="n">
+      <c r="D14" s="1" t="n">
         <v>0.0158730158730159</v>
       </c>
-      <c r="E14" s="0" t="n">
+      <c r="E14" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="F14" s="0" t="n">
+      <c r="F14" s="1" t="n">
         <v>0.0206349206349206</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="n">
+      <c r="A15" s="1" t="n">
         <v>32</v>
       </c>
-      <c r="B15" s="0" t="n">
+      <c r="B15" s="1" t="n">
         <v>0.0111111111111111</v>
       </c>
-      <c r="C15" s="0" t="n">
+      <c r="C15" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="D15" s="0" t="n">
+      <c r="D15" s="1" t="n">
         <v>0.0190476190476191</v>
       </c>
-      <c r="E15" s="0" t="n">
+      <c r="E15" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="F15" s="0" t="n">
+      <c r="F15" s="1" t="n">
         <v>0.0238095238095238</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="n">
+      <c r="A16" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="0" t="n">
+      <c r="B16" s="1" t="n">
         <v>0.0206349206349206</v>
       </c>
-      <c r="C16" s="0" t="n">
+      <c r="C16" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="D16" s="0" t="n">
+      <c r="D16" s="1" t="n">
         <v>0.0190476190476191</v>
       </c>
-      <c r="E16" s="0" t="n">
+      <c r="E16" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="F16" s="0" t="n">
+      <c r="F16" s="1" t="n">
         <v>0.0158730158730159</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="n">
+      <c r="A17" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="B17" s="0" t="n">
+      <c r="B17" s="1" t="n">
         <v>0.0206349206349206</v>
       </c>
-      <c r="C17" s="0" t="n">
+      <c r="C17" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="D17" s="0" t="n">
+      <c r="D17" s="1" t="n">
         <v>0.0190476190476191</v>
       </c>
-      <c r="E17" s="0" t="n">
+      <c r="E17" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="F17" s="0" t="n">
+      <c r="F17" s="1" t="n">
         <v>0.0142857142857143</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="n">
+      <c r="A18" s="1" t="n">
         <v>34</v>
       </c>
-      <c r="B18" s="0" t="n">
+      <c r="B18" s="1" t="n">
         <v>0.0190476190476191</v>
       </c>
     </row>
@@ -656,180 +660,180 @@
   <dimension ref="A1:F9"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="n">
+      <c r="A1" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B1" s="0" t="n">
+      <c r="B1" s="1" t="n">
         <v>41</v>
       </c>
-      <c r="C1" s="0" t="n">
+      <c r="C1" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="D1" s="0" t="n">
+      <c r="D1" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="E1" s="0" t="n">
+      <c r="E1" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="F1" s="0" t="n">
+      <c r="F1" s="1" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>38</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="C2" s="0" t="n">
+      <c r="C2" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2" s="1" t="n">
         <v>39</v>
       </c>
-      <c r="E2" s="0" t="n">
+      <c r="E2" s="1" t="n">
         <v>43</v>
       </c>
-      <c r="F2" s="0" t="n">
+      <c r="F2" s="1" t="n">
         <v>45</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="C3" s="0" t="n">
+      <c r="C3" s="1" t="n">
         <v>32</v>
       </c>
-      <c r="D3" s="0" t="n">
+      <c r="D3" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="E3" s="0" t="n">
+      <c r="E3" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="F3" s="0" t="n">
+      <c r="F3" s="1" t="n">
         <v>34</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="1" t="n">
         <v>52</v>
       </c>
-      <c r="C4" s="0" t="n">
+      <c r="C4" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="D4" s="0" t="n">
+      <c r="D4" s="1" t="n">
         <v>42</v>
       </c>
-      <c r="E4" s="0" t="n">
+      <c r="E4" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="F4" s="0" t="n">
+      <c r="F4" s="1" t="n">
         <v>23</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>37</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="C5" s="0" t="n">
+      <c r="C5" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D5" s="0" t="n">
+      <c r="D5" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="E5" s="0" t="n">
+      <c r="E5" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="0" t="n">
+      <c r="F5" s="1" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="1" t="n">
         <v>29</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="C6" s="0" t="n">
+      <c r="C6" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="D6" s="0" t="n">
+      <c r="D6" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="E6" s="0" t="n">
+      <c r="E6" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="F6" s="0" t="n">
+      <c r="F6" s="1" t="n">
         <v>18</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="1" t="n">
         <v>48</v>
       </c>
-      <c r="B7" s="0" t="n">
+      <c r="B7" s="1" t="n">
         <v>49</v>
       </c>
-      <c r="C7" s="0" t="n">
+      <c r="C7" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="D7" s="0" t="n">
+      <c r="D7" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="E7" s="0" t="n">
+      <c r="E7" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="F7" s="0" t="n">
+      <c r="F7" s="1" t="n">
         <v>46</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+      <c r="A8" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="0" t="n">
+      <c r="B8" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="C8" s="0" t="n">
+      <c r="C8" s="1" t="n">
         <v>44</v>
       </c>
-      <c r="D8" s="0" t="n">
+      <c r="D8" s="1" t="n">
         <v>47</v>
       </c>
-      <c r="E8" s="0" t="n">
+      <c r="E8" s="1" t="n">
         <v>33</v>
       </c>
-      <c r="F8" s="0" t="n">
+      <c r="F8" s="1" t="n">
         <v>51</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+      <c r="A9" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="B9" s="0" t="n">
+      <c r="B9" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="C9" s="0" t="n">
+      <c r="C9" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="D9" s="0" t="n">
+      <c r="D9" s="1" t="n">
         <v>24</v>
       </c>
     </row>
@@ -853,554 +857,554 @@
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="n">
+      <c r="A1" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B1" s="0" t="n">
+      <c r="B1" s="1" t="n">
         <v>41</v>
       </c>
-      <c r="C1" s="0" t="n">
+      <c r="C1" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="D1" s="0" t="n">
+      <c r="D1" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="E1" s="0" t="n">
+      <c r="E1" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="F1" s="0" t="n">
+      <c r="F1" s="1" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>38</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="C2" s="0" t="n">
+      <c r="C2" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2" s="1" t="n">
         <v>39</v>
       </c>
-      <c r="E2" s="0" t="n">
+      <c r="E2" s="1" t="n">
         <v>43</v>
       </c>
-      <c r="F2" s="0" t="n">
+      <c r="F2" s="1" t="n">
         <v>45</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="C3" s="0" t="n">
+      <c r="C3" s="1" t="n">
         <v>32</v>
       </c>
-      <c r="D3" s="0" t="n">
+      <c r="D3" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="E3" s="0" t="n">
+      <c r="E3" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="F3" s="0" t="n">
+      <c r="F3" s="1" t="n">
         <v>34</v>
       </c>
-      <c r="AU3" s="0" t="n">
+      <c r="AU3" s="1" t="n">
         <v>34</v>
       </c>
-      <c r="AV3" s="0" t="n">
+      <c r="AV3" s="1" t="n">
         <v>34</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="1" t="n">
         <v>52</v>
       </c>
-      <c r="C4" s="0" t="n">
+      <c r="C4" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="D4" s="0" t="n">
+      <c r="D4" s="1" t="n">
         <v>42</v>
       </c>
-      <c r="E4" s="0" t="n">
+      <c r="E4" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="F4" s="0" t="n">
+      <c r="F4" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="AU4" s="0" t="n">
+      <c r="AU4" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="AV4" s="0" t="n">
+      <c r="AV4" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="AW4" s="0" t="n">
+      <c r="AW4" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="AX4" s="0" t="n">
+      <c r="AX4" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="AY4" s="0" t="n">
+      <c r="AY4" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="AZ4" s="0" t="n">
+      <c r="AZ4" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="BA4" s="0" t="n">
+      <c r="BA4" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="BB4" s="0" t="n">
+      <c r="BB4" s="1" t="n">
         <v>23</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>37</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="C5" s="0" t="n">
+      <c r="C5" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D5" s="0" t="n">
+      <c r="D5" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="E5" s="0" t="n">
+      <c r="E5" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="0" t="n">
+      <c r="F5" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="AU5" s="0" t="n">
+      <c r="AU5" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="AV5" s="0" t="n">
+      <c r="AV5" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="AW5" s="0" t="n">
+      <c r="AW5" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AX5" s="0" t="n">
+      <c r="AX5" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AY5" s="0" t="n">
+      <c r="AY5" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AZ5" s="0" t="n">
+      <c r="AZ5" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="BA5" s="0" t="n">
+      <c r="BA5" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="BB5" s="0" t="n">
+      <c r="BB5" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="BC5" s="0" t="n">
+      <c r="BC5" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="BD5" s="0" t="n">
+      <c r="BD5" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="BE5" s="0" t="n">
+      <c r="BE5" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="BF5" s="0" t="n">
+      <c r="BF5" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="BG5" s="0" t="n">
+      <c r="BG5" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="BH5" s="0" t="n">
+      <c r="BH5" s="1" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="1" t="n">
         <v>29</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="C6" s="0" t="n">
+      <c r="C6" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="D6" s="0" t="n">
+      <c r="D6" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="E6" s="0" t="n">
+      <c r="E6" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="F6" s="0" t="n">
+      <c r="F6" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="AU6" s="0" t="n">
+      <c r="AU6" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="AV6" s="0" t="n">
+      <c r="AV6" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="AW6" s="0" t="n">
+      <c r="AW6" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="AX6" s="0" t="n">
+      <c r="AX6" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="AY6" s="0" t="n">
+      <c r="AY6" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="AZ6" s="0" t="n">
+      <c r="AZ6" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="BA6" s="0" t="n">
+      <c r="BA6" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="BB6" s="0" t="n">
+      <c r="BB6" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="BC6" s="0" t="n">
+      <c r="BC6" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="BD6" s="0" t="n">
+      <c r="BD6" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="BE6" s="0" t="n">
+      <c r="BE6" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="BF6" s="0" t="n">
+      <c r="BF6" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="BG6" s="0" t="n">
+      <c r="BG6" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="BH6" s="0" t="n">
+      <c r="BH6" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="BI6" s="0" t="n">
+      <c r="BI6" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="BJ6" s="0" t="n">
+      <c r="BJ6" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="BK6" s="0" t="n">
+      <c r="BK6" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="BL6" s="0" t="n">
+      <c r="BL6" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="BM6" s="0" t="n">
+      <c r="BM6" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="BN6" s="0" t="n">
+      <c r="BN6" s="1" t="n">
         <v>18</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="1" t="n">
         <v>48</v>
       </c>
-      <c r="B7" s="0" t="n">
+      <c r="B7" s="1" t="n">
         <v>49</v>
       </c>
-      <c r="C7" s="0" t="n">
+      <c r="C7" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="D7" s="0" t="n">
+      <c r="D7" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="E7" s="0" t="n">
+      <c r="E7" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="F7" s="0" t="n">
+      <c r="F7" s="1" t="n">
         <v>46</v>
       </c>
-      <c r="AU7" s="0" t="n">
+      <c r="AU7" s="1" t="n">
         <v>49</v>
       </c>
-      <c r="AV7" s="0" t="n">
+      <c r="AV7" s="1" t="n">
         <v>49</v>
       </c>
-      <c r="AW7" s="0" t="n">
+      <c r="AW7" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="AX7" s="0" t="n">
+      <c r="AX7" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="AY7" s="0" t="n">
+      <c r="AY7" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="AZ7" s="0" t="n">
+      <c r="AZ7" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="BA7" s="0" t="n">
+      <c r="BA7" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="BB7" s="0" t="n">
+      <c r="BB7" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="BC7" s="0" t="n">
+      <c r="BC7" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="BD7" s="0" t="n">
+      <c r="BD7" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="BE7" s="0" t="n">
+      <c r="BE7" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="BF7" s="0" t="n">
+      <c r="BF7" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="BG7" s="0" t="n">
+      <c r="BG7" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="BH7" s="0" t="n">
+      <c r="BH7" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="BI7" s="0" t="n">
+      <c r="BI7" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="BJ7" s="0" t="n">
+      <c r="BJ7" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="BK7" s="0" t="n">
+      <c r="BK7" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="BL7" s="0" t="n">
+      <c r="BL7" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="BM7" s="0" t="n">
+      <c r="BM7" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="BN7" s="0" t="n">
+      <c r="BN7" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="BO7" s="0" t="n">
+      <c r="BO7" s="1" t="n">
         <v>46</v>
       </c>
-      <c r="BP7" s="0" t="n">
+      <c r="BP7" s="1" t="n">
         <v>46</v>
       </c>
-      <c r="BQ7" s="0" t="n">
+      <c r="BQ7" s="1" t="n">
         <v>46</v>
       </c>
-      <c r="BR7" s="0" t="n">
+      <c r="BR7" s="1" t="n">
         <v>46</v>
       </c>
-      <c r="BS7" s="0" t="n">
+      <c r="BS7" s="1" t="n">
         <v>46</v>
       </c>
-      <c r="BT7" s="0" t="n">
+      <c r="BT7" s="1" t="n">
         <v>46</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+      <c r="A8" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="0" t="n">
+      <c r="B8" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="C8" s="0" t="n">
+      <c r="C8" s="1" t="n">
         <v>44</v>
       </c>
-      <c r="D8" s="0" t="n">
+      <c r="D8" s="1" t="n">
         <v>47</v>
       </c>
-      <c r="E8" s="0" t="n">
+      <c r="E8" s="1" t="n">
         <v>33</v>
       </c>
-      <c r="F8" s="0" t="n">
+      <c r="F8" s="1" t="n">
         <v>51</v>
       </c>
-      <c r="AU8" s="0" t="n">
+      <c r="AU8" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="AV8" s="0" t="n">
+      <c r="AV8" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="AW8" s="0" t="n">
+      <c r="AW8" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="AX8" s="0" t="n">
+      <c r="AX8" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="AY8" s="0" t="n">
+      <c r="AY8" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="AZ8" s="0" t="n">
+      <c r="AZ8" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="BA8" s="0" t="n">
+      <c r="BA8" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="BB8" s="0" t="n">
+      <c r="BB8" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="BC8" s="0" t="n">
+      <c r="BC8" s="1" t="n">
         <v>44</v>
       </c>
-      <c r="BD8" s="0" t="n">
+      <c r="BD8" s="1" t="n">
         <v>44</v>
       </c>
-      <c r="BE8" s="0" t="n">
+      <c r="BE8" s="1" t="n">
         <v>44</v>
       </c>
-      <c r="BF8" s="0" t="n">
+      <c r="BF8" s="1" t="n">
         <v>44</v>
       </c>
-      <c r="BG8" s="0" t="n">
+      <c r="BG8" s="1" t="n">
         <v>44</v>
       </c>
-      <c r="BH8" s="0" t="n">
+      <c r="BH8" s="1" t="n">
         <v>44</v>
       </c>
-      <c r="BI8" s="0" t="n">
+      <c r="BI8" s="1" t="n">
         <v>47</v>
       </c>
-      <c r="BJ8" s="0" t="n">
+      <c r="BJ8" s="1" t="n">
         <v>47</v>
       </c>
-      <c r="BK8" s="0" t="n">
+      <c r="BK8" s="1" t="n">
         <v>47</v>
       </c>
-      <c r="BL8" s="0" t="n">
+      <c r="BL8" s="1" t="n">
         <v>47</v>
       </c>
-      <c r="BM8" s="0" t="n">
+      <c r="BM8" s="1" t="n">
         <v>47</v>
       </c>
-      <c r="BN8" s="0" t="n">
+      <c r="BN8" s="1" t="n">
         <v>47</v>
       </c>
-      <c r="BO8" s="0" t="n">
+      <c r="BO8" s="1" t="n">
         <v>33</v>
       </c>
-      <c r="BP8" s="0" t="n">
+      <c r="BP8" s="1" t="n">
         <v>33</v>
       </c>
-      <c r="BQ8" s="0" t="n">
+      <c r="BQ8" s="1" t="n">
         <v>33</v>
       </c>
-      <c r="BR8" s="0" t="n">
+      <c r="BR8" s="1" t="n">
         <v>33</v>
       </c>
-      <c r="BS8" s="0" t="n">
+      <c r="BS8" s="1" t="n">
         <v>33</v>
       </c>
-      <c r="BT8" s="0" t="n">
+      <c r="BT8" s="1" t="n">
         <v>33</v>
       </c>
-      <c r="BU8" s="0" t="n">
+      <c r="BU8" s="1" t="n">
         <v>51</v>
       </c>
-      <c r="BV8" s="0" t="n">
+      <c r="BV8" s="1" t="n">
         <v>51</v>
       </c>
-      <c r="BW8" s="0" t="n">
+      <c r="BW8" s="1" t="n">
         <v>51</v>
       </c>
-      <c r="BX8" s="0" t="n">
+      <c r="BX8" s="1" t="n">
         <v>51</v>
       </c>
-      <c r="BY8" s="0" t="n">
+      <c r="BY8" s="1" t="n">
         <v>51</v>
       </c>
-      <c r="BZ8" s="0" t="n">
+      <c r="BZ8" s="1" t="n">
         <v>51</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+      <c r="A9" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="B9" s="0" t="n">
+      <c r="B9" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="C9" s="0" t="n">
+      <c r="C9" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="D9" s="0" t="n">
+      <c r="D9" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="AW9" s="0" t="n">
+      <c r="AW9" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="AX9" s="0" t="n">
+      <c r="AX9" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="AY9" s="0" t="n">
+      <c r="AY9" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="AZ9" s="0" t="n">
+      <c r="AZ9" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="BA9" s="0" t="n">
+      <c r="BA9" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="BB9" s="0" t="n">
+      <c r="BB9" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="BC9" s="0" t="n">
+      <c r="BC9" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="BD9" s="0" t="n">
+      <c r="BD9" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="BE9" s="0" t="n">
+      <c r="BE9" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="BF9" s="0" t="n">
+      <c r="BF9" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="BG9" s="0" t="n">
+      <c r="BG9" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="BH9" s="0" t="n">
+      <c r="BH9" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="BI9" s="0" t="n">
+      <c r="BI9" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="BJ9" s="0" t="n">
+      <c r="BJ9" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="BK9" s="0" t="n">
+      <c r="BK9" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="BL9" s="0" t="n">
+      <c r="BL9" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="BM9" s="0" t="n">
+      <c r="BM9" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="BN9" s="0" t="n">
+      <c r="BN9" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="BO9" s="0" t="n">
+      <c r="BO9" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="BP9" s="0" t="n">
+      <c r="BP9" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="BQ9" s="0" t="n">
+      <c r="BQ9" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="BR9" s="0" t="n">
+      <c r="BR9" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="BS9" s="0" t="n">
+      <c r="BS9" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="BT9" s="0" t="n">
+      <c r="BT9" s="1" t="n">
         <v>24</v>
       </c>
     </row>
